--- a/Practice Budget Expenses Revenue Conversion/2026 P&L by Month.xlsx
+++ b/Practice Budget Expenses Revenue Conversion/2026 P&L by Month.xlsx
@@ -584,48 +584,48 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee ($99/mo)</t>
+          <t>SEO &amp; Web Services ($99/mo)</t>
         </is>
       </c>
       <c r="B6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;B$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;B$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>198</v>
       </c>
       <c r="C6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;C$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;C$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;D$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;D$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>396</v>
       </c>
       <c r="E6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;E$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;E$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;F$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;F$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>198</v>
       </c>
       <c r="G6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;G$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;G$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>198</v>
       </c>
       <c r="H6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;H$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;H$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
+        <v>198</v>
       </c>
       <c r="I6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;I$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;I$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
+        <v>297</v>
       </c>
       <c r="J6" s="9">
-        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"Membership Fee",'Revenue Detail'!$A:$A,"&gt;="&amp;J$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v/>
+        <f>SUMIFS('Revenue Detail'!$D:$D,'Revenue Detail'!$C:$C,"SEO &amp; Web Services",'Revenue Detail'!$A:$A,"&gt;="&amp;J$4,'Revenue Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
+        <v>0</v>
       </c>
       <c r="K6" s="9">
         <f>SUM(B6:J6)</f>
-        <v/>
+        <v>1485</v>
       </c>
     </row>
     <row r="7">
@@ -636,43 +636,43 @@
       </c>
       <c r="B7" s="10">
         <f>SUM(B6:B6)</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="C7" s="10">
         <f>SUM(C6:C6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D7" s="10">
         <f>SUM(D6:D6)</f>
-        <v/>
+        <v>396</v>
       </c>
       <c r="E7" s="10">
         <f>SUM(E6:E6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F7" s="10">
         <f>SUM(F6:F6)</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="G7" s="10">
         <f>SUM(G6:G6)</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="H7" s="10">
         <f>SUM(H6:H6)</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="I7" s="10">
         <f>SUM(I6:I6)</f>
-        <v/>
+        <v>297</v>
       </c>
       <c r="J7" s="10">
         <f>SUM(J6:J6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K7" s="10">
         <f>SUM(K6:K6)</f>
-        <v/>
+        <v>1485</v>
       </c>
     </row>
     <row r="9">
@@ -700,43 +700,43 @@
       </c>
       <c r="B10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="C10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="D10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="E10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="G10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="H10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="I10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="J10" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="K10" s="9">
         <f>SUM(B10:J10)</f>
-        <v/>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
@@ -747,43 +747,43 @@
       </c>
       <c r="B11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="H11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="J11" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K11" s="9">
         <f>SUM(B11:J11)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -794,43 +794,43 @@
       </c>
       <c r="B12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="D12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="E12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="F12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="G12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="H12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="I12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="J12" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="K12" s="9">
         <f>SUM(B12:J12)</f>
-        <v/>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -841,43 +841,43 @@
       </c>
       <c r="B13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="E13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="F13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="G13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="J13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="K13" s="9">
         <f>SUM(B13:J13)</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -888,43 +888,43 @@
       </c>
       <c r="B14" s="10">
         <f>SUM(B10:B13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="C14" s="10">
         <f>SUM(C10:C13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="D14" s="10">
         <f>SUM(D10:D13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="E14" s="10">
         <f>SUM(E10:E13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="F14" s="10">
         <f>SUM(F10:F13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="G14" s="10">
         <f>SUM(G10:G13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="H14" s="10">
         <f>SUM(H10:H13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="I14" s="10">
         <f>SUM(I10:I13)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="J14" s="10">
         <f>SUM(J10:J13)</f>
-        <v/>
+        <v>61</v>
       </c>
       <c r="K14" s="10">
         <f>SUM(K10:K13)</f>
-        <v/>
+        <v>445</v>
       </c>
     </row>
     <row r="16">
@@ -935,43 +935,43 @@
       </c>
       <c r="B16" s="12">
         <f>B7-B14</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="C16" s="12">
         <f>C7-C14</f>
-        <v/>
+        <v>-48</v>
       </c>
       <c r="D16" s="12">
         <f>D7-D14</f>
-        <v/>
+        <v>348</v>
       </c>
       <c r="E16" s="12">
         <f>E7-E14</f>
-        <v/>
+        <v>-48</v>
       </c>
       <c r="F16" s="12">
         <f>F7-F14</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G16" s="12">
         <f>G7-G14</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="H16" s="12">
         <f>H7-H14</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="I16" s="12">
         <f>I7-I14</f>
-        <v/>
+        <v>249</v>
       </c>
       <c r="J16" s="12">
         <f>J7-J14</f>
-        <v/>
+        <v>-61</v>
       </c>
       <c r="K16" s="12">
         <f>K7-K14</f>
-        <v/>
+        <v>1040</v>
       </c>
     </row>
     <row r="19">
@@ -984,14 +984,14 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>- Membership Fee revenue is pulled directly from the recorded Invoice rows in Revenue-source.xlsx (actual invoice dates, not evenly smoothed).</t>
+          <t>- SEO &amp; Web Services revenue is pulled directly from the recorded Invoice rows in Revenue-source.xlsx (actual invoice dates, not evenly smoothed).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Feb and Apr show $0 because no invoice was recorded those months in the source file; Sep shows $0 because no Sep membership invoice has been recorded yet.</t>
+          <t xml:space="preserve">  Feb and Apr show $0 because no invoice was recorded those months in the source file; Sep shows $0 because no Sep SEO &amp; Web Services invoice has been recorded yet.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D8" s="17" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D12" s="17" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D14" s="17" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Membership Fee</t>
+          <t>SEO &amp; Web Services</t>
         </is>
       </c>
       <c r="D16" s="17" t="n">

--- a/Practice Budget Expenses Revenue Conversion/2026 P&L by Month.xlsx
+++ b/Practice Budget Expenses Revenue Conversion/2026 P&L by Month.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -110,30 +115,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,10 +506,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -678,7 +685,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cost of Goods Sold (COGS)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -695,336 +702,515 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t xml:space="preserve">    Seobility</t>
         </is>
       </c>
       <c r="B10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="C10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="D10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="E10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="F10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="G10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="H10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="I10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="J10" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
+        <v>10</v>
+      </c>
+      <c r="K10" s="9">
+        <f>SUM(B10:J10)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ubersuggest</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="C11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="D11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="E11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="F11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="G11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="H11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="I11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="J11" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
+        <v>12</v>
+      </c>
+      <c r="K11" s="9">
+        <f>SUM(B11:J11)</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>SEO Tools (GroupRB:SEO Tools)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>SUM(B10:B11)</f>
+        <v>22</v>
+      </c>
+      <c r="C12" s="9">
+        <f>SUM(C10:C11)</f>
+        <v>22</v>
+      </c>
+      <c r="D12" s="9">
+        <f>SUM(D10:D11)</f>
+        <v>22</v>
+      </c>
+      <c r="E12" s="9">
+        <f>SUM(E10:E11)</f>
+        <v>22</v>
+      </c>
+      <c r="F12" s="9">
+        <f>SUM(F10:F11)</f>
+        <v>22</v>
+      </c>
+      <c r="G12" s="9">
+        <f>SUM(G10:G11)</f>
+        <v>22</v>
+      </c>
+      <c r="H12" s="9">
+        <f>SUM(H10:H11)</f>
+        <v>22</v>
+      </c>
+      <c r="I12" s="9">
+        <f>SUM(I10:I11)</f>
+        <v>22</v>
+      </c>
+      <c r="J12" s="9">
+        <f>SUM(J10:J11)</f>
+        <v>22</v>
+      </c>
+      <c r="K12" s="9">
+        <f>SUM(K10:K11)</f>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Hosting (GroupRB:Hosting)</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
         <v>20</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
         <v>20</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
         <v>20</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
         <v>20</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
         <v>20</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
         <v>20</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
         <v>20</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
         <v>20</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J13" s="9">
         <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
         <v>30</v>
       </c>
-      <c r="K10" s="9">
-        <f>SUM(B10:J10)</f>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Seobility</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="C11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="D11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="E11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="F11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="G11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="H11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="I11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="J11" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Seobility",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v>10</v>
-      </c>
-      <c r="K11" s="9">
-        <f>SUM(B11:J11)</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Ubersuggest</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="C12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="D12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="E12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="F12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="G12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="H12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="I12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="J12" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Ubersuggest",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v>12</v>
-      </c>
-      <c r="K12" s="9">
-        <f>SUM(B12:J12)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="B13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="C13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="D13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="E13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="F13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="G13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="H13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="I13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
-        <v>6</v>
-      </c>
-      <c r="J13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Billing Fee",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
-        <v>9</v>
-      </c>
       <c r="K13" s="9">
         <f>SUM(B13:J13)</f>
-        <v>57</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Total COGS</t>
         </is>
       </c>
       <c r="B14" s="10">
-        <f>SUM(B10:B13)</f>
-        <v>48</v>
+        <f>SUM(B12:B13)</f>
+        <v>42</v>
       </c>
       <c r="C14" s="10">
-        <f>SUM(C10:C13)</f>
-        <v>48</v>
+        <f>SUM(C12:C13)</f>
+        <v>42</v>
       </c>
       <c r="D14" s="10">
-        <f>SUM(D10:D13)</f>
-        <v>48</v>
+        <f>SUM(D12:D13)</f>
+        <v>42</v>
       </c>
       <c r="E14" s="10">
-        <f>SUM(E10:E13)</f>
-        <v>48</v>
+        <f>SUM(E12:E13)</f>
+        <v>42</v>
       </c>
       <c r="F14" s="10">
-        <f>SUM(F10:F13)</f>
-        <v>48</v>
+        <f>SUM(F12:F13)</f>
+        <v>42</v>
       </c>
       <c r="G14" s="10">
-        <f>SUM(G10:G13)</f>
-        <v>48</v>
+        <f>SUM(G12:G13)</f>
+        <v>42</v>
       </c>
       <c r="H14" s="10">
-        <f>SUM(H10:H13)</f>
-        <v>48</v>
+        <f>SUM(H12:H13)</f>
+        <v>42</v>
       </c>
       <c r="I14" s="10">
-        <f>SUM(I10:I13)</f>
-        <v>48</v>
+        <f>SUM(I12:I13)</f>
+        <v>42</v>
       </c>
       <c r="J14" s="10">
-        <f>SUM(J10:J13)</f>
-        <v>61</v>
+        <f>SUM(J12:J13)</f>
+        <v>52</v>
       </c>
       <c r="K14" s="10">
-        <f>SUM(K10:K13)</f>
-        <v>445</v>
+        <f>SUM(K12:K13)</f>
+        <v>388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B16" s="12">
         <f>B7-B14</f>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C16" s="12">
         <f>C7-C14</f>
-        <v>-48</v>
+        <v>-42</v>
       </c>
       <c r="D16" s="12">
         <f>D7-D14</f>
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E16" s="12">
         <f>E7-E14</f>
-        <v>-48</v>
+        <v>-42</v>
       </c>
       <c r="F16" s="12">
         <f>F7-F14</f>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G16" s="12">
         <f>G7-G14</f>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H16" s="12">
         <f>H7-H14</f>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I16" s="12">
         <f>I7-I14</f>
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="J16" s="12">
         <f>J7-J14</f>
-        <v>-61</v>
+        <v>-52</v>
       </c>
       <c r="K16" s="12">
         <f>K7-K14</f>
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Bank Fees (GroupRB:Bank Fees)</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="C19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="D19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="E19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="F19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="H19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="I19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
+        <v>6</v>
+      </c>
+      <c r="J19" s="9">
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
+        <v>9</v>
+      </c>
+      <c r="K19" s="9">
+        <f>SUM(B19:J19)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B20" s="10">
+        <f>SUM(B19:B19)</f>
+        <v>6</v>
+      </c>
+      <c r="C20" s="10">
+        <f>SUM(C19:C19)</f>
+        <v>6</v>
+      </c>
+      <c r="D20" s="10">
+        <f>SUM(D19:D19)</f>
+        <v>6</v>
+      </c>
+      <c r="E20" s="10">
+        <f>SUM(E19:E19)</f>
+        <v>6</v>
+      </c>
+      <c r="F20" s="10">
+        <f>SUM(F19:F19)</f>
+        <v>6</v>
+      </c>
+      <c r="G20" s="10">
+        <f>SUM(G19:G19)</f>
+        <v>6</v>
+      </c>
+      <c r="H20" s="10">
+        <f>SUM(H19:H19)</f>
+        <v>6</v>
+      </c>
+      <c r="I20" s="10">
+        <f>SUM(I19:I19)</f>
+        <v>6</v>
+      </c>
+      <c r="J20" s="10">
+        <f>SUM(J19:J19)</f>
+        <v>9</v>
+      </c>
+      <c r="K20" s="10">
+        <f>SUM(K19:K19)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>B16-B20</f>
+        <v>150</v>
+      </c>
+      <c r="C22" s="13">
+        <f>C16-C20</f>
+        <v>-48</v>
+      </c>
+      <c r="D22" s="13">
+        <f>D16-D20</f>
+        <v>348</v>
+      </c>
+      <c r="E22" s="13">
+        <f>E16-E20</f>
+        <v>-48</v>
+      </c>
+      <c r="F22" s="13">
+        <f>F16-F20</f>
+        <v>150</v>
+      </c>
+      <c r="G22" s="13">
+        <f>G16-G20</f>
+        <v>150</v>
+      </c>
+      <c r="H22" s="13">
+        <f>H16-H20</f>
+        <v>150</v>
+      </c>
+      <c r="I22" s="13">
+        <f>I16-I20</f>
+        <v>249</v>
+      </c>
+      <c r="J22" s="13">
+        <f>J16-J20</f>
+        <v>-61</v>
+      </c>
+      <c r="K22" s="13">
+        <f>K16-K20</f>
         <v>1040</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Notes / assumptions:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>- SEO &amp; Web Services revenue is pulled directly from the recorded Invoice rows in Revenue-source.xlsx (actual invoice dates, not evenly smoothed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Feb and Apr show $0 because no invoice was recorded those months in the source file; Sep shows $0 because no Sep SEO &amp; Web Services invoice has been recorded yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>- Hosting, Seobility, Ubersuggest and Billing Fee are GroupRB out-of-pocket costs to deliver Parts of Practice, entered per the schedule you gave:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hosting $10/mo and Billing Fee $3/mo — Andy Studer &amp; Gratitude Jan-Sep, Guidance Through Grief Sep only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Seobility $5/mo and Ubersuggest $6/mo — Andy Studer &amp; Gratitude only, Jan-Sep (not billed for Grief).</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>- "Billing Fee" is my label for the $3/mo charge described as "monthly billing charge" — rename in the Expense Detail sheet if you use a different name internally.</t>
+          <t>Notes / assumptions:</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>- SEO &amp; Web Services revenue is pulled directly from the recorded Invoice rows in Revenue-source.xlsx (actual invoice dates, not evenly smoothed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Feb and Apr show $0 because no invoice was recorded those months in the source file; Sep shows $0 because no Sep SEO &amp; Web Services invoice has been recorded yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>- Hosting and SEO Tools (Seobility + Ubersuggest) are classified as COGS: direct, per-client costs of delivering the SEO &amp; Web Services product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>- Bank Fees ($3/mo QuickBooks Payments processing fee) is classified as an Operating Expense, not COGS, since it is a cost of collecting payment, not of delivering the service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>- Schedule: Hosting $10/mo and Bank Fees $3/mo — Andy Studer &amp; Gratitude Jan-Sep, Guidance Through Grief Sep only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Seobility $5/mo and Ubersuggest $6/mo — Andy Studer &amp; Gratitude only, Jan-Sep (not billed for Grief).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>- The Expense Detail sheet has a "GL Account (Patriot)" column showing which account to code each transaction to when categorizing in Patriot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>- Patriot true parent/child sub-accounts (e.g. GroupRB as parent of Hosting/SEO Tools/Bank Fees) require the Accounting Premium plan (up to 8 levels).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  On the Basic plan, naming an account "GroupRB:Hosting" creates a flat account with that literal name — it will not nest or roll up in reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>- All monthly charges are dated the 1st of the month per your instructions ("billed on the 1st").</t>
         </is>
@@ -1051,29 +1237,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1086,12 +1272,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1104,12 +1290,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="17" t="n">
         <v>46083</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1122,12 +1308,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>46083</v>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1140,12 +1326,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1158,12 +1344,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1176,12 +1362,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="17" t="n">
         <v>46146</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1194,12 +1380,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="17" t="n">
         <v>46146</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1212,12 +1398,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="17" t="n">
         <v>46181</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1230,12 +1416,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="17" t="n">
         <v>46181</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1248,12 +1434,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="17" t="n">
         <v>46204</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1266,12 +1452,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="17" t="n">
         <v>46204</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1284,12 +1470,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="17" t="n">
         <v>46239</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1302,12 +1488,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="17" t="n">
         <v>46239</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1320,12 +1506,12 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="17" t="n">
         <v>46239</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1338,7 +1524,7 @@
           <t>SEO &amp; Web Services</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>99</v>
       </c>
     </row>
@@ -1353,39 +1539,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>GL Account (Patriot)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1395,15 +1587,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1413,15 +1610,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1434,12 +1636,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1452,12 +1659,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1470,12 +1682,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1488,12 +1705,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1506,12 +1728,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
-        <v>6</v>
+      <c r="D8" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="19" t="n">
         <v>46023</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1524,12 +1751,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>6</v>
+      <c r="D9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1539,15 +1771,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,15 +1794,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1578,12 +1820,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1596,12 +1843,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1614,12 +1866,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1632,12 +1889,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1650,12 +1912,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
-        <v>6</v>
+      <c r="D16" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="19" t="n">
         <v>46054</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1668,12 +1935,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
-        <v>6</v>
+      <c r="D17" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1683,15 +1955,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1701,15 +1978,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1722,12 +2004,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1740,12 +2027,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,12 +2050,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1776,12 +2073,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1794,12 +2096,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
-        <v>6</v>
+      <c r="D24" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="19" t="n">
         <v>46082</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1812,12 +2119,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
-        <v>6</v>
+      <c r="D25" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1827,15 +2139,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1845,15 +2162,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1866,12 +2188,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1884,12 +2211,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1902,12 +2234,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1920,12 +2257,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1938,12 +2280,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n">
-        <v>6</v>
+      <c r="D32" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="19" t="n">
         <v>46113</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,12 +2303,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n">
-        <v>6</v>
+      <c r="D33" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1971,15 +2323,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1989,15 +2346,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2010,12 +2372,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2028,12 +2395,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2046,12 +2418,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2064,12 +2441,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2082,12 +2464,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D40" s="17" t="n">
-        <v>6</v>
+      <c r="D40" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="19" t="n">
         <v>46143</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2100,12 +2487,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D41" s="17" t="n">
-        <v>6</v>
+      <c r="D41" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2115,15 +2507,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2133,15 +2530,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2154,12 +2556,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2172,12 +2579,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2190,12 +2602,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2208,12 +2625,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2226,12 +2648,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D48" s="17" t="n">
-        <v>6</v>
+      <c r="D48" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="19" t="n">
         <v>46174</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2244,12 +2671,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D49" s="17" t="n">
-        <v>6</v>
+      <c r="D49" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2259,15 +2691,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2277,15 +2714,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2298,12 +2740,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2316,12 +2763,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2334,12 +2786,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2352,12 +2809,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,12 +2832,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D56" s="17" t="n">
-        <v>6</v>
+      <c r="D56" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="19" t="n">
         <v>46204</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2388,12 +2855,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D57" s="17" t="n">
-        <v>6</v>
+      <c r="D57" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2403,15 +2875,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2421,15 +2898,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2442,12 +2924,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2460,12 +2947,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2478,12 +2970,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2496,12 +2993,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2514,12 +3016,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D64" s="17" t="n">
-        <v>6</v>
+      <c r="D64" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="19" t="n">
         <v>46235</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2532,12 +3039,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D65" s="17" t="n">
-        <v>6</v>
+      <c r="D65" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2547,15 +3059,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="n">
+      <c r="A67" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2565,15 +3082,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="n">
+      <c r="A68" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2583,15 +3105,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Billing Fee</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="n">
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="n">
         <v>3</v>
       </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Bank Fees</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="n">
+      <c r="A69" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2604,12 +3131,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="n">
+      <c r="A70" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2622,12 +3154,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="n">
+      <c r="A71" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2640,12 +3177,17 @@
           <t>Hosting</t>
         </is>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:Hosting</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="n">
+      <c r="A72" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2658,12 +3200,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="n">
+      <c r="A73" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2676,12 +3223,17 @@
           <t>Seobility</t>
         </is>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="18" t="n">
         <v>5</v>
       </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="n">
+      <c r="A74" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2694,12 +3246,17 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D74" s="17" t="n">
-        <v>6</v>
+      <c r="D74" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="n">
+      <c r="A75" s="19" t="n">
         <v>46266</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2712,8 +3269,13 @@
           <t>Ubersuggest</t>
         </is>
       </c>
-      <c r="D75" s="17" t="n">
-        <v>6</v>
+      <c r="D75" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>GroupRB:SEO Tools</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Practice Budget Expenses Revenue Conversion/2026 P&L by Month.xlsx
+++ b/Practice Budget Expenses Revenue Conversion/2026 P&L by Month.xlsx
@@ -796,7 +796,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>SEO Tools (GroupRB:SEO Tools)</t>
+          <t>SEO Tools</t>
         </is>
       </c>
       <c r="B12" s="9">
@@ -843,43 +843,43 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Hosting (GroupRB:Hosting)</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="B13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
         <v>20</v>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
         <v>20</v>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
         <v>20</v>
       </c>
       <c r="E13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
         <v>20</v>
       </c>
       <c r="F13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
         <v>20</v>
       </c>
       <c r="G13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
         <v>20</v>
       </c>
       <c r="H13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
         <v>20</v>
       </c>
       <c r="I13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
         <v>20</v>
       </c>
       <c r="J13" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Hosting Fees",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
         <v>30</v>
       </c>
       <c r="K13" s="9">
@@ -1001,43 +1001,43 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Bank Fees (GroupRB:Bank Fees)</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="B19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;B$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(B$4,1))</f>
         <v>6</v>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;C$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(C$4,1))</f>
         <v>6</v>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;D$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(D$4,1))</f>
         <v>6</v>
       </c>
       <c r="E19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;E$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(E$4,1))</f>
         <v>6</v>
       </c>
       <c r="F19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;F$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(F$4,1))</f>
         <v>6</v>
       </c>
       <c r="G19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;G$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(G$4,1))</f>
         <v>6</v>
       </c>
       <c r="H19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;H$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(H$4,1))</f>
         <v>6</v>
       </c>
       <c r="I19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;I$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(I$4,1))</f>
         <v>6</v>
       </c>
       <c r="J19" s="9">
-        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Fees",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
+        <f>SUMIFS('Expense Detail'!$D:$D,'Expense Detail'!$C:$C,"Bank Processing Fees",'Expense Detail'!$A:$A,"&gt;="&amp;J$4,'Expense Detail'!$A:$A,"&lt;"&amp;EDATE(J$4,1))</f>
         <v>9</v>
       </c>
       <c r="K19" s="9">
@@ -1163,49 +1163,49 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>- Hosting and SEO Tools (Seobility + Ubersuggest) are classified as COGS: direct, per-client costs of delivering the SEO &amp; Web Services product.</t>
+          <t>- Hosting Fees and SEO Tools (Seobility + Ubersuggest) are classified as COGS: direct, per-client costs of delivering the SEO &amp; Web Services product.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>- Bank Fees ($3/mo QuickBooks Payments processing fee) is classified as an Operating Expense, not COGS, since it is a cost of collecting payment, not of delivering the service.</t>
+          <t xml:space="preserve">  In Patriot they are subaccounts of Cost of Goods Sold, matching the chart of accounts you set up (Cost of Goods Sold &gt; SEO Tools, Hosting Fees).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>- Schedule: Hosting $10/mo and Bank Fees $3/mo — Andy Studer &amp; Gratitude Jan-Sep, Guidance Through Grief Sep only.</t>
+          <t>- Bank Processing Fees ($3/mo QuickBooks Payments processing fee) is classified as an Operating Expense, not COGS, since it is a cost of collecting</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Seobility $5/mo and Ubersuggest $6/mo — Andy Studer &amp; Gratitude only, Jan-Sep (not billed for Grief).</t>
+          <t xml:space="preserve">  payment, not of delivering the service. Uses your existing Bank Processing Fees account rather than a new one.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>- The Expense Detail sheet has a "GL Account (Patriot)" column showing which account to code each transaction to when categorizing in Patriot.</t>
+          <t>- Schedule: Hosting Fees $10/mo and Bank Processing Fees $3/mo — Andy Studer &amp; Gratitude Jan-Sep, Guidance Through Grief Sep only.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>- Patriot true parent/child sub-accounts (e.g. GroupRB as parent of Hosting/SEO Tools/Bank Fees) require the Accounting Premium plan (up to 8 levels).</t>
+          <t xml:space="preserve">  Seobility $5/mo and Ubersuggest $6/mo — Andy Studer &amp; Gratitude only, Jan-Sep (not billed for Grief).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  On the Basic plan, naming an account "GroupRB:Hosting" creates a flat account with that literal name — it will not nest or roll up in reports.</t>
+          <t>- The Expense Detail sheet has a "GL Account (Patriot)" column showing which account to code each transaction to when categorizing in Patriot.</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D2" s="18" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E2" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D3" s="18" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D4" s="18" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D5" s="18" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="E47" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="E51" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D66" s="18" t="n">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D67" s="18" t="n">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
       <c r="D68" s="18" t="n">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Bank Fees</t>
+          <t>Bank Processing Fees</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D69" s="18" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D70" s="18" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Hosting Fees</t>
         </is>
       </c>
       <c r="D71" s="18" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:Hosting</t>
+          <t>Hosting Fees (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>GroupRB:SEO Tools</t>
+          <t>SEO Tools (sub of Cost of Goods Sold)</t>
         </is>
       </c>
     </row>
